--- a/dist/plugins/blend-kit/skills/blend-generate-task/_kit/skills/blend-generate-test-spec/assets/test-report-block-template.vi.xlsx
+++ b/dist/plugins/blend-kit/skills/blend-generate-task/_kit/skills/blend-generate-test-spec/assets/test-report-block-template.vi.xlsx
@@ -1,15 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <ns0:workbookPr filterPrivacy="1"/>
-  <ns0:sheets>
-    <ns0:sheet name="Tổng quan" sheetId="1" state="visible" ns1:id="rId1"/>
-    <ns0:sheet name="Testcases" sheetId="2" state="visible" ns1:id="rId2"/>
-  </ns0:sheets>
-  <ns0:definedNames>
-    <ns0:definedName name="_xlnm.Print_Area" localSheetId="1">'Testcases'!$A$1:$E$21</ns0:definedName>
-  </ns0:definedNames>
-</ns0:workbook>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet name="Tổng quan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Kiểm thử" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tổng quan'!$A$29:$C$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tổng quan'!$A$1:$C$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Kiểm thử'!$A$1:$F$93</definedName>
+  </definedNames>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -77,6 +79,23 @@
       <b val="1"/>
       <color rgb="00172033"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00172033"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001D4ED8"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00172033"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="9">
@@ -122,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -144,11 +163,109 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E2EC"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9E2EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E2EC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E2EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9E2EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9E2EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -289,6 +406,93 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="8" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="8" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="8" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -561,9 +765,9 @@
   <sheetPr>
     <tabColor rgb="00334155"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -580,7 +784,7 @@
       <c r="B1" s="3" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="3" t="n"/>
+      <c r="A2" s="3" t="inlineStr"/>
       <c r="B2" s="3" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
@@ -590,98 +794,119 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Chức năng</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>SYN-SC synthetic rule lifecycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Phiên bản kiểm thử</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>compact-r1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Lần kiểm thử</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n"/>
-      <c r="C6" s="36" t="n"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
+      <c r="B6" s="57" t="inlineStr"/>
+      <c r="C6" s="71" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Phiên bản ứng dụng</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="36" t="n"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
+      <c r="B7" s="57" t="inlineStr"/>
+      <c r="C7" s="71" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Môi trường</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="36" t="n"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
+      <c r="B8" s="57" t="inlineStr"/>
+      <c r="C8" s="71" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Người thực hiện</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="36" t="n"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
+      <c r="B9" s="57" t="inlineStr"/>
+      <c r="C9" s="71" t="n"/>
+    </row>
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Thời điểm thực hiện (kèm múi giờ)</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="36" t="n"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
+      <c r="B10" s="57" t="inlineStr"/>
+      <c r="C10" s="71" t="n"/>
+    </row>
+    <row r="11" ht="78" customHeight="1">
       <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Phạm vi</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
+      <c r="B11" s="56" t="inlineStr">
+        <is>
+          <t>SYN:O1–O8; boundary, deletion, incomplete/stale rule, AND controls
+Chuẩn bị: TD-SC create/verify/reset once per variant; G-PREP retains unknown entry/readback seams
+Điều kiện bắt đầu: G-PREP resolved before readiness; do not infer from source fixture
+Điều kiện kết thúc: Every requested variant/checkpoint observed; no invented PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Ngoài phạm vi</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
+      <c r="B12" s="56" t="inlineStr">
+        <is>
+          <t>None of the eight source obligations; real BLEND QA is outside this synthetic fixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="61" customHeight="1">
       <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Giới hạn</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>Chuẩn bị theo testcase</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B13" s="56" t="inlineStr">
+        <is>
+          <t>G-PREP: concrete browser/request seams are not verified
+1 khoảng trống được giữ trong Điều kiện kiểm thử của các testcase tương ứng.
+5 testcase chưa có URL màn hình tương đối được xác minh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="34" t="inlineStr"/>
+      <c r="B14" s="56" t="inlineStr"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="37" t="inlineStr">
@@ -697,8 +922,8 @@
           <t>Số TC</t>
         </is>
       </c>
-      <c r="B16" s="39">
-        <f>COUNTA(A30:A30)</f>
+      <c r="B16" s="58">
+        <f>1</f>
         <v/>
       </c>
     </row>
@@ -708,8 +933,8 @@
           <t>Số biến thể</t>
         </is>
       </c>
-      <c r="B17" s="39">
-        <f>COUNTA('Kiểm thử'!$A$5:$A$5)</f>
+      <c r="B17" s="58">
+        <f>2</f>
         <v/>
       </c>
     </row>
@@ -719,8 +944,8 @@
           <t>TC PASS</t>
         </is>
       </c>
-      <c r="B18" s="39">
-        <f>0</f>
+      <c r="B18" s="58">
+        <f>COUNTIF(C30:C30,"Đạt")</f>
         <v/>
       </c>
     </row>
@@ -730,8 +955,8 @@
           <t>TC FAIL</t>
         </is>
       </c>
-      <c r="B19" s="39">
-        <f>0</f>
+      <c r="B19" s="58">
+        <f>COUNTIF(C30:C30,"Không đạt")</f>
         <v/>
       </c>
     </row>
@@ -741,8 +966,8 @@
           <t>Biến thể bị chặn</t>
         </is>
       </c>
-      <c r="B20" s="39">
-        <f>0</f>
+      <c r="B20" s="58">
+        <f>SUM('Testcases'!B90)</f>
         <v/>
       </c>
     </row>
@@ -752,8 +977,8 @@
           <t>Biến thể không thực hiện</t>
         </is>
       </c>
-      <c r="B21" s="39">
-        <f>0</f>
+      <c r="B21" s="58">
+        <f>SUM('Testcases'!B91)</f>
         <v/>
       </c>
     </row>
@@ -763,8 +988,8 @@
           <t>Biến thể chưa thực hiện</t>
         </is>
       </c>
-      <c r="B22" s="39">
-        <f>0</f>
+      <c r="B22" s="58">
+        <f>SUM('Testcases'!B92)</f>
         <v/>
       </c>
     </row>
@@ -774,7 +999,7 @@
           <t>TC đã đánh giá</t>
         </is>
       </c>
-      <c r="B23" s="39">
+      <c r="B23" s="58">
         <f>B18+B19</f>
         <v/>
       </c>
@@ -785,7 +1010,7 @@
           <t>Tỷ lệ PASS theo TC</t>
         </is>
       </c>
-      <c r="B24" s="40">
+      <c r="B24" s="59">
         <f>IF(B23=0,"Chưa có dữ liệu",B18/B23)</f>
         <v/>
       </c>
@@ -796,8 +1021,8 @@
           <t>Tiến độ theo TC</t>
         </is>
       </c>
-      <c r="B25" s="40">
-        <f>IF(B17=0,"Chưa có dữ liệu",B23/B17)</f>
+      <c r="B25" s="59">
+        <f>IF(B16=0,"Chưa có dữ liệu",B23/B16)</f>
         <v/>
       </c>
     </row>
@@ -807,8 +1032,8 @@
           <t>TC chưa PASS</t>
         </is>
       </c>
-      <c r="B26" s="39">
-        <f>B17-B18</f>
+      <c r="B26" s="58">
+        <f>B16-B18</f>
         <v/>
       </c>
     </row>
@@ -818,8 +1043,8 @@
           <t>Trạng thái biến thể không hợp lệ</t>
         </is>
       </c>
-      <c r="B27" s="39">
-        <f>B17-SUM(0,0,0,0,0)</f>
+      <c r="B27" s="58">
+        <f>B17-SUM(B20:B22,SUM('Testcases'!B88),SUM('Testcases'!B89))</f>
         <v/>
       </c>
     </row>
@@ -844,11 +1069,8 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="3" t="n"/>
-      <c r="B30" s="3" t="n"/>
-    </row>
   </sheetData>
+  <autoFilter ref="A29:C30"/>
   <mergeCells count="12">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B6:C6"/>
@@ -863,7 +1085,9 @@
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B12:C12"/>
   </mergeCells>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -871,287 +1095,64 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0064748B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr summaryBelow="0" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="44" t="inlineStr">
-        <is>
-          <t>Mẫu bố cục TC</t>
-        </is>
-      </c>
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>Kiểm thử chi tiết</t>
+        </is>
+      </c>
+      <c r="B1" s="78" t="n"/>
+      <c r="C1" s="78" t="n"/>
+      <c r="D1" s="78" t="n"/>
+      <c r="E1" s="78" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="45" t="inlineStr">
-        <is>
-          <t>Block dưới đây chỉ minh họa cách trình bày, không phải testcase thật. Generator sẽ xóa block mẫu trước khi ghi dữ liệu nguồn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="12" customHeight="1"/>
+      <c r="A2" s="79" t="inlineStr"/>
+      <c r="B2" s="78" t="n"/>
+      <c r="C2" s="78" t="n"/>
+      <c r="D2" s="78" t="n"/>
+      <c r="E2" s="78" t="n"/>
+    </row>
+    <row r="3" ht="12" customHeight="1">
+      <c r="A3" s="78" t="n"/>
+      <c r="B3" s="78" t="n"/>
+      <c r="C3" s="78" t="n"/>
+      <c r="D3" s="78" t="n"/>
+      <c r="E3" s="78" t="n"/>
+    </row>
     <row r="4" ht="8" customHeight="1">
-      <c r="A4" s="20" t="n"/>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="46" t="inlineStr">
-        <is>
-          <t>[TC-ID] — [Tiêu đề testcase]</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="47" t="inlineStr">
-        <is>
-          <t>Trạng thái</t>
-        </is>
-      </c>
-      <c r="B6" s="48" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="C6" s="26" t="n"/>
-      <c r="D6" s="26" t="n"/>
-      <c r="E6" s="26" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="47" t="inlineStr">
-        <is>
-          <t>Màn hình / chức năng</t>
-        </is>
-      </c>
-      <c r="B7" s="49" t="inlineStr">
-        <is>
-          <t>[Tên màn hình / chức năng]</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="n"/>
-      <c r="D7" s="47" t="inlineStr">
-        <is>
-          <t>Đường dẫn</t>
-        </is>
-      </c>
-      <c r="E7" s="49" t="inlineStr">
-        <is>
-          <t>[/relative/path]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="50" t="inlineStr">
-        <is>
-          <t>Điều kiện kiểm thử</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="n"/>
-      <c r="C8" s="30" t="n"/>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="30" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="47" t="inlineStr">
-        <is>
-          <t>Cấu hình</t>
-        </is>
-      </c>
-      <c r="B9" s="49" t="inlineStr">
-        <is>
-          <t>• [Điều kiện hoặc trạng thái ban đầu]</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="n"/>
-      <c r="D9" s="26" t="n"/>
-      <c r="E9" s="26" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="47" t="inlineStr">
-        <is>
-          <t>Vai trò / quyền</t>
-        </is>
-      </c>
-      <c r="B10" s="49" t="inlineStr">
-        <is>
-          <t>• [Vai trò và quyền cần thiết]</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="47" t="inlineStr">
-        <is>
-          <t>Dữ liệu test</t>
-        </is>
-      </c>
-      <c r="B11" s="49" t="inlineStr">
-        <is>
-          <t>• [Dữ liệu và giá trị test]</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="n"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="50" t="inlineStr">
-        <is>
-          <t>Thao tác</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="n"/>
-      <c r="C12" s="30" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="47" t="inlineStr">
-        <is>
-          <t>Step 1</t>
-        </is>
-      </c>
-      <c r="B13" s="49" t="inlineStr">
-        <is>
-          <t>[Thao tác đầu tiên]</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="26" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="47" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="B14" s="49" t="inlineStr">
-        <is>
-          <t>[Thao tác tiếp theo]</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="26" t="n"/>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="50" t="inlineStr">
-        <is>
-          <t>Kết quả mong đợi</t>
-        </is>
-      </c>
-      <c r="B15" s="30" t="n"/>
-      <c r="C15" s="30" t="n"/>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="30" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="47" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B16" s="49" t="inlineStr">
-        <is>
-          <t>[Kết quả có thể quan sát và so sánh]</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="26" t="n"/>
-      <c r="E16" s="26" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="47" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B17" s="49" t="inlineStr">
-        <is>
-          <t>[Hành vi hoặc dữ liệu phải giữ nguyên]</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="n"/>
-      <c r="D17" s="26" t="n"/>
-      <c r="E17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="50" t="inlineStr">
-        <is>
-          <t>Kết quả thực tế</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="n"/>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="30" t="n"/>
-    </row>
-    <row r="19" ht="64" customHeight="1">
-      <c r="A19" s="43" t="n"/>
-      <c r="B19" s="26" t="n"/>
-      <c r="C19" s="26" t="n"/>
-      <c r="D19" s="26" t="n"/>
-      <c r="E19" s="26" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="47" t="inlineStr">
-        <is>
-          <t>Ảnh minh chứng</t>
-        </is>
-      </c>
-      <c r="B20" s="26" t="n"/>
-      <c r="C20" s="26" t="n"/>
-      <c r="D20" s="26" t="n"/>
-      <c r="E20" s="26" t="n"/>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="43" t="n"/>
-      <c r="B21" s="26" t="n"/>
-      <c r="C21" s="26" t="n"/>
-      <c r="D21" s="26" t="n"/>
-      <c r="E21" s="26" t="n"/>
+      <c r="A4" s="80" t="n"/>
+      <c r="B4" s="78" t="n"/>
+      <c r="C4" s="78" t="n"/>
+      <c r="D4" s="78" t="n"/>
+      <c r="E4" s="78" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B7:C7"/>
+  <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"Đạt,Không đạt,Bị chặn,Không thực hiện,Chưa thực hiện"</formula1>
     </dataValidation>
   </dataValidations>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/dist/plugins/blend-kit/skills/blend-generate-task/_kit/skills/blend-generate-test-spec/assets/test-report-block-template.vi.xlsx
+++ b/dist/plugins/blend-kit/skills/blend-generate-task/_kit/skills/blend-generate-test-spec/assets/test-report-block-template.vi.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <sheets>
-    <sheet name="Tổng quan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Kiểm thử" sheetId="2" state="visible" r:id="rId2"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tổng quan'!$A$29:$C$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tổng quan'!$A$1:$C$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Kiểm thử'!$A$1:$F$93</definedName>
-  </definedNames>
-</workbook>
+<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:workbookPr filterPrivacy="1"/>
+  <s:sheets>
+    <s:sheet name="Tổng quan" sheetId="1" state="visible" r:id="rId1"/>
+    <s:sheet name="Kiểm thử" sheetId="2" state="visible" r:id="rId2"/>
+  </s:sheets>
+  <s:definedNames>
+    <s:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tổng quan'!$A$29:$C$30</s:definedName>
+    <s:definedName name="_xlnm.Print_Area" localSheetId="0">'Tổng quan'!$A$1:$C$30</s:definedName>
+    <s:definedName name="_xlnm.Print_Area" localSheetId="1">'Kiểm thử'!$A$1:$E$13</s:definedName>
+  </s:definedNames>
+</s:workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="&quot;&#10;&quot;General;&quot;&#10;&quot;-General;&quot;&#10;&quot;General;&quot;&#10;&quot;@"/>
+    <numFmt numFmtId="166" formatCode="&quot;&#10;&quot;#,##0;&quot;&#10;&quot;-#,##0;&quot;&#10;&quot;#,##0;&quot;&#10;&quot;@"/>
+    <numFmt numFmtId="167" formatCode="&quot;&#10;&quot;0.0%;&quot;&#10;&quot;-0.0%;&quot;&#10;&quot;0.0%;&quot;&#10;&quot;@"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -97,8 +100,14 @@
       <color rgb="00172033"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -140,6 +149,11 @@
         <fgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0017324D"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="12">
     <border>
@@ -265,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -493,6 +507,94 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -776,100 +878,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="97" t="inlineStr">
         <is>
           <t>Báo cáo kiểm thử</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="98" t="n"/>
+      <c r="C1" s="99" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
       <c r="A2" s="3" t="inlineStr"/>
       <c r="B2" s="3" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="100" t="inlineStr">
         <is>
           <t>Nhập lần kiểm thử, phiên bản ứng dụng, môi trường, người và thời điểm thực hiện.</t>
         </is>
       </c>
+      <c r="C3" s="99" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="101" t="inlineStr">
         <is>
           <t>Chức năng</t>
         </is>
       </c>
-      <c r="B4" s="56" t="inlineStr">
+      <c r="B4" s="102" t="inlineStr">
         <is>
           <t>SYN-SC synthetic rule lifecycle</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="101" t="inlineStr">
         <is>
           <t>Phiên bản kiểm thử</t>
         </is>
       </c>
-      <c r="B5" s="56" t="inlineStr">
+      <c r="B5" s="102" t="inlineStr">
         <is>
           <t>compact-r1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="101" t="inlineStr">
         <is>
           <t>Lần kiểm thử</t>
         </is>
       </c>
-      <c r="B6" s="57" t="inlineStr"/>
+      <c r="B6" s="103" t="inlineStr"/>
       <c r="C6" s="71" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="101" t="inlineStr">
         <is>
           <t>Phiên bản ứng dụng</t>
         </is>
       </c>
-      <c r="B7" s="57" t="inlineStr"/>
+      <c r="B7" s="103" t="inlineStr"/>
       <c r="C7" s="71" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="101" t="inlineStr">
         <is>
           <t>Môi trường</t>
         </is>
       </c>
-      <c r="B8" s="57" t="inlineStr"/>
+      <c r="B8" s="103" t="inlineStr"/>
       <c r="C8" s="71" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="101" t="inlineStr">
         <is>
           <t>Người thực hiện</t>
         </is>
       </c>
-      <c r="B9" s="57" t="inlineStr"/>
+      <c r="B9" s="103" t="inlineStr"/>
       <c r="C9" s="71" t="n"/>
     </row>
     <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="101" t="inlineStr">
         <is>
           <t>Thời điểm thực hiện (kèm múi giờ)</t>
         </is>
       </c>
-      <c r="B10" s="57" t="inlineStr"/>
+      <c r="B10" s="103" t="inlineStr"/>
       <c r="C10" s="71" t="n"/>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="101" t="inlineStr">
         <is>
           <t>Phạm vi</t>
         </is>
       </c>
-      <c r="B11" s="56" t="inlineStr">
+      <c r="B11" s="102" t="inlineStr">
         <is>
           <t>SYN:O1–O8; boundary, deletion, incomplete/stale rule, AND controls
 Chuẩn bị: TD-SC create/verify/reset once per variant; G-PREP retains unknown entry/readback seams
@@ -879,24 +983,24 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="101" t="inlineStr">
         <is>
           <t>Ngoài phạm vi</t>
         </is>
       </c>
-      <c r="B12" s="56" t="inlineStr">
+      <c r="B12" s="102" t="inlineStr">
         <is>
           <t>None of the eight source obligations; real BLEND QA is outside this synthetic fixture</t>
         </is>
       </c>
     </row>
     <row r="13" ht="61" customHeight="1">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="101" t="inlineStr">
         <is>
           <t>Giới hạn</t>
         </is>
       </c>
-      <c r="B13" s="56" t="inlineStr">
+      <c r="B13" s="102" t="inlineStr">
         <is>
           <t>G-PREP: concrete browser/request seams are not verified
 1 khoảng trống được giữ trong Điều kiện kiểm thử của các testcase tương ứng.
@@ -909,161 +1013,174 @@
       <c r="B14" s="56" t="inlineStr"/>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="104" t="inlineStr">
         <is>
           <t>Tiến độ và kết quả</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
+      <c r="B15" s="104" t="n"/>
+      <c r="C15" s="99" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="98" t="inlineStr">
         <is>
           <t>Số TC</t>
         </is>
       </c>
-      <c r="B16" s="58">
+      <c r="B16" s="105">
         <f>1</f>
         <v/>
       </c>
+      <c r="C16" s="99" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="98" t="inlineStr">
         <is>
           <t>Số biến thể</t>
         </is>
       </c>
-      <c r="B17" s="58">
+      <c r="B17" s="105">
         <f>2</f>
         <v/>
       </c>
+      <c r="C17" s="99" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="98" t="inlineStr">
         <is>
           <t>TC PASS</t>
         </is>
       </c>
-      <c r="B18" s="58">
+      <c r="B18" s="105">
         <f>COUNTIF(C30:C30,"Đạt")</f>
         <v/>
       </c>
+      <c r="C18" s="99" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="98" t="inlineStr">
         <is>
           <t>TC FAIL</t>
         </is>
       </c>
-      <c r="B19" s="58">
+      <c r="B19" s="105">
         <f>COUNTIF(C30:C30,"Không đạt")</f>
         <v/>
       </c>
+      <c r="C19" s="99" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="38" t="inlineStr">
+      <c r="A20" s="98" t="inlineStr">
         <is>
           <t>Biến thể bị chặn</t>
         </is>
       </c>
-      <c r="B20" s="58">
+      <c r="B20" s="105">
         <f>SUM('Testcases'!B90)</f>
         <v/>
       </c>
+      <c r="C20" s="99" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="98" t="inlineStr">
         <is>
           <t>Biến thể không thực hiện</t>
         </is>
       </c>
-      <c r="B21" s="58">
+      <c r="B21" s="105">
         <f>SUM('Testcases'!B91)</f>
         <v/>
       </c>
+      <c r="C21" s="99" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="98" t="inlineStr">
         <is>
           <t>Biến thể chưa thực hiện</t>
         </is>
       </c>
-      <c r="B22" s="58">
+      <c r="B22" s="105">
         <f>SUM('Testcases'!B92)</f>
         <v/>
       </c>
+      <c r="C22" s="99" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="38" t="inlineStr">
+      <c r="A23" s="98" t="inlineStr">
         <is>
           <t>TC đã đánh giá</t>
         </is>
       </c>
-      <c r="B23" s="58">
+      <c r="B23" s="105">
         <f>B18+B19</f>
         <v/>
       </c>
+      <c r="C23" s="99" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="38" t="inlineStr">
+      <c r="A24" s="98" t="inlineStr">
         <is>
           <t>Tỷ lệ PASS theo TC</t>
         </is>
       </c>
-      <c r="B24" s="59">
+      <c r="B24" s="106">
         <f>IF(B23=0,"Chưa có dữ liệu",B18/B23)</f>
         <v/>
       </c>
+      <c r="C24" s="99" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="38" t="inlineStr">
+      <c r="A25" s="98" t="inlineStr">
         <is>
           <t>Tiến độ theo TC</t>
         </is>
       </c>
-      <c r="B25" s="59">
+      <c r="B25" s="106">
         <f>IF(B16=0,"Chưa có dữ liệu",B23/B16)</f>
         <v/>
       </c>
+      <c r="C25" s="99" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="38" t="inlineStr">
+      <c r="A26" s="98" t="inlineStr">
         <is>
           <t>TC chưa PASS</t>
         </is>
       </c>
-      <c r="B26" s="58">
+      <c r="B26" s="105">
         <f>B16-B18</f>
         <v/>
       </c>
+      <c r="C26" s="99" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="38" t="inlineStr">
+      <c r="A27" s="98" t="inlineStr">
         <is>
           <t>Trạng thái biến thể không hợp lệ</t>
         </is>
       </c>
-      <c r="B27" s="58">
+      <c r="B27" s="105">
         <f>B17-SUM(B20:B22,SUM('Testcases'!B88),SUM('Testcases'!B89))</f>
         <v/>
       </c>
+      <c r="C27" s="99" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="3" t="n"/>
       <c r="B28" s="3" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="37" t="inlineStr">
+      <c r="A29" s="104" t="inlineStr">
         <is>
           <t>Mã TC</t>
         </is>
       </c>
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B29" s="104" t="inlineStr">
         <is>
           <t>Testcase</t>
         </is>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C29" s="104" t="inlineStr">
         <is>
           <t>Trạng thái tổng hợp</t>
         </is>
@@ -1092,67 +1209,190 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0064748B"/>
-    <outlinePr summaryBelow="0" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="77" t="inlineStr">
-        <is>
-          <t>Kiểm thử chi tiết</t>
-        </is>
-      </c>
-      <c r="B1" s="78" t="n"/>
-      <c r="C1" s="78" t="n"/>
-      <c r="D1" s="78" t="n"/>
-      <c r="E1" s="78" t="n"/>
-    </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="79" t="inlineStr"/>
-      <c r="B2" s="78" t="n"/>
-      <c r="C2" s="78" t="n"/>
-      <c r="D2" s="78" t="n"/>
-      <c r="E2" s="78" t="n"/>
-    </row>
-    <row r="3" ht="12" customHeight="1">
-      <c r="A3" s="78" t="n"/>
-      <c r="B3" s="78" t="n"/>
-      <c r="C3" s="78" t="n"/>
-      <c r="D3" s="78" t="n"/>
-      <c r="E3" s="78" t="n"/>
-    </row>
-    <row r="4" ht="8" customHeight="1">
-      <c r="A4" s="80" t="n"/>
-      <c r="B4" s="78" t="n"/>
-      <c r="C4" s="78" t="n"/>
-      <c r="D4" s="78" t="n"/>
-      <c r="E4" s="78" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
-      <formula1>"Đạt,Không đạt,Bị chặn,Không thực hiện,Chưa thực hiện"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="0"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
+<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:sheetPr>
+    <s:tabColor rgb="0064748B"/>
+    <s:outlinePr summaryBelow="0" summaryRight="1"/>
+    <s:pageSetUpPr fitToPage="1"/>
+  </s:sheetPr>
+  <s:dimension ref="A1:E13"/>
+  <s:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <s:cols>
+    <s:col width="24" customWidth="1" min="1" max="1"/>
+    <s:col width="35" customWidth="1" min="2" max="2"/>
+    <s:col width="45" customWidth="1" min="3" max="3"/>
+    <s:col width="35" customWidth="1" min="4" max="4"/>
+    <s:col width="19" customWidth="1" min="5" max="5"/>
+    <s:col width="18" customWidth="1" min="6" max="6"/>
+    <s:col width="28" customWidth="1" min="7" max="7"/>
+  </s:cols>
+  <s:sheetData>
+    <s:row r="1" ht="32" customHeight="1">
+      <s:c r="A1" s="107" t="inlineStr">
+        <s:is>
+          <s:t>Kiểm thử chi tiết</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B1" s="99" t="n"/>
+      <s:c r="C1" s="99" t="n"/>
+      <s:c r="D1" s="99" t="n"/>
+      <s:c r="E1" s="99" t="n"/>
+    </s:row>
+    <s:row r="2" hidden="1" ht="42" customHeight="1">
+      <s:c r="A2" s="79" t="inlineStr"/>
+    </s:row>
+    <s:row r="3" hidden="1" ht="12" customHeight="1">
+      <s:c r="A3" s="78" t="n"/>
+      <s:c r="B3" s="78" t="n"/>
+      <s:c r="C3" s="78" t="n"/>
+      <s:c r="D3" s="78" t="n"/>
+      <s:c r="E3" s="78" t="n"/>
+    </s:row>
+    <s:row r="4" hidden="1" ht="8" customHeight="1">
+      <s:c r="A4" s="80" t="n"/>
+      <s:c r="B4" s="78" t="n"/>
+      <s:c r="C4" s="78" t="n"/>
+      <s:c r="D4" s="78" t="n"/>
+      <s:c r="E4" s="78" t="n"/>
+    </s:row>
+    <s:row r="5" ht="30" customHeight="1">
+      <s:c r="A5" s="108" t="inlineStr">
+        <s:is>
+          <s:t>[Mã TC] — [Tên tình huống]</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="6" ht="30" customHeight="1">
+      <s:c r="A6" s="102" t="inlineStr">
+        <s:is>
+          <s:t>Kết quả tình huống</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B6" s="102" t="inlineStr">
+        <s:is>
+          <s:t>Chưa thực hiện</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C6" s="99" t="n"/>
+      <s:c r="D6" s="99" t="n"/>
+      <s:c r="E6" s="99" t="n"/>
+    </s:row>
+    <s:row r="7" ht="42" customHeight="1">
+      <s:c r="A7" s="102" t="inlineStr">
+        <s:is>
+          <s:t>Điều kiện</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B7" s="102" t="inlineStr">
+        <s:is>
+          <s:t>[Trạng thái ban đầu và dữ liệu dùng chung]</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="8" ht="30" customHeight="1">
+      <s:c r="A8" s="102" t="inlineStr">
+        <s:is>
+          <s:t>Bước</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B8" s="102" t="inlineStr">
+        <s:is>
+          <s:t>Thao tác chung</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="9" ht="42" customHeight="1">
+      <s:c r="A9" s="102" t="inlineStr">
+        <s:is>
+          <s:t>Bước 1</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B9" s="102" t="inlineStr">
+        <s:is>
+          <s:t>[Thao tác dùng chung]</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="10" ht="28" customHeight="1">
+      <s:c r="A10" s="80" t="inlineStr">
+        <s:is>
+          <s:t>Trường hợp</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B10" s="80" t="inlineStr">
+        <s:is>
+          <s:t>Dữ liệu / thao tác riêng</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C10" s="80" t="inlineStr">
+        <s:is>
+          <s:t>Kết quả mong đợi</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D10" s="80" t="inlineStr">
+        <s:is>
+          <s:t>Kết quả thực tế</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E10" s="80" t="inlineStr">
+        <s:is>
+          <s:t>Đánh giá</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="11" ht="3" customHeight="1">
+      <s:c r="D11" s="36" t="n"/>
+      <s:c r="E11" s="36" t="n"/>
+    </s:row>
+    <s:row r="12" ht="42" customHeight="1">
+      <s:c r="A12" s="83" t="inlineStr">
+        <s:is>
+          <s:t>Hủy xóa (cancel)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B12" s="83" t="inlineStr">
+        <s:is>
+          <s:r>
+            <s:rPr>
+              <s:b val="1"/>
+            </s:rPr>
+            <s:t>Chọn Hủy（キャンセル）</s:t>
+          </s:r>
+          <s:r>
+            <s:t xml:space="preserve"> trong hộp xác nhận.</s:t>
+          </s:r>
+        </s:is>
+      </s:c>
+      <s:c r="C12" s="83" t="inlineStr">
+        <s:is>
+          <s:t>Danh sách vẫn có đủ hai quy tắc.</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D12" s="109" t="inlineStr"/>
+      <s:c r="E12" s="109" t="inlineStr">
+        <s:is>
+          <s:t>Chưa thực hiện</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="13" ht="30" customHeight="1">
+      <s:c r="A13" s="102" t="inlineStr">
+        <s:is>
+          <s:t>Ảnh minh chứng — Chưa có ảnh</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+  </s:sheetData>
+  <s:mergeCells count="6">
+    <s:mergeCell ref="B9:E9"/>
+    <s:mergeCell ref="B8:E8"/>
+    <s:mergeCell ref="A2:E2"/>
+    <s:mergeCell ref="B7:E7"/>
+    <s:mergeCell ref="A5:E5"/>
+    <s:mergeCell ref="A13:E13"/>
+  </s:mergeCells>
+  <s:printOptions horizontalCentered="0"/>
+  <s:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <s:pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</s:worksheet>
 </file>